--- a/reports/expense_report.xlsx
+++ b/reports/expense_report.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -452,111 +449,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46201</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>travel</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>petrol</t>
+          <t>daily groceries</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46199</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>momoj</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46194</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>pizza</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>shopping</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>shoes</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>46185</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>medical</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>fever</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>46178</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>bills</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>350</v>
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
